--- a/outputs/evaluation/requirement/validation/gemini-3-5-flash-lite/CF_M04/second/CF_M04_req_eval.xlsx
+++ b/outputs/evaluation/requirement/validation/gemini-3-5-flash-lite/CF_M04/second/CF_M04_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9738</v>
       </c>
     </row>
@@ -755,10 +763,6 @@
           <t>The system shall allow a Localboss user to receive intelligent response suggestions to reviews, to answer them faster, more accurately, and more professionally.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>FR</t>
@@ -772,10 +776,6 @@
           <t>I want to receive intelligent suggestions for responding to reviews.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -806,10 +806,6 @@
           <t>The system shall allow a delegated user to log in via their email address or phone number, so that they can access the application without needing a main account.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>FR</t>
@@ -824,10 +820,6 @@
 phone number</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -858,10 +850,6 @@
           <t>The system shall allow an authenticated user to view a Home screen with relevant information about their business, to quickly check the status of their activity.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>FR</t>
@@ -876,10 +864,6 @@
 of my business</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -910,10 +894,6 @@
           <t>The system shall allow a user to access the application menu from different screens, to facilitate navigation and access to main functionalities.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>FR</t>
@@ -927,10 +907,6 @@
           <t>I want to be able to access the application menu from different screens</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -961,10 +937,6 @@
           <t>The system shall allow a user to view images and videos associated with a review, to have more context about the customer's opinion.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>FR</t>
@@ -978,10 +950,6 @@
           <t xml:space="preserve"> I want to be able to see images and videos associated with a review</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1012,14 +980,11 @@
           <t>Access to functionalities requires valid authentication and unauthorized access is not allowed.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>R_35</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1033,14 +998,11 @@
           <t>Access to features requires valid authentication and is not allows unauthorized access.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>CF_M04_R35</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1076,9 +1038,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1102,8 +1061,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1134,14 +1091,11 @@
           <t>The multimedia content must be displayed below the review text.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1155,14 +1109,11 @@
           <t>Multimedia content should be displayed below the review text.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CF_M04_R20</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1193,14 +1144,11 @@
           <t>The application visualizes and functions correctly on Android and iOS emulators and physical devices.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_31</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1214,14 +1162,11 @@
           <t>The application displays and works correctly on emulators and physical Android and iOS devices.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CF_M04_R31</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1252,14 +1197,11 @@
           <t>The system must display loading and error states when necessary.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1273,14 +1215,11 @@
           <t>The system must display loading and error statuses when necessary.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>CF_M04_R07</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1316,9 +1255,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1342,8 +1278,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1374,14 +1308,11 @@
           <t>Access to the menu must be done via the user's profile picture.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>R_25</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1395,14 +1326,11 @@
           <t>Access to the menu must be done through the user's profile image.</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>CF_M04_R25</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1433,14 +1361,11 @@
           <t>Images must be navigable via horizontal scroll.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1454,14 +1379,11 @@
           <t>The images must be navigable via horizontal scrolling.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>CF_M04_R20</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1492,14 +1414,11 @@
           <t>The suggestion must be generated automatically when opening the response modal.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1513,14 +1432,11 @@
           <t>The suggestion should be generated automatically when opening the response modal.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1556,9 +1472,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1582,8 +1495,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1614,14 +1525,11 @@
           <t>Upon clicking an image or video, it must be displayed in full screen.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1635,14 +1543,11 @@
           <t>When clicking an image or video, it must be displayed in full screen.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CF_M04_R20</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1673,14 +1578,11 @@
           <t>If Cintia is active, the system must show a response suggestion.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1694,14 +1596,11 @@
           <t>If Cintia is active, the system must display a response suggestion.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1732,14 +1631,11 @@
           <t>If the user does not have Cintia credits, they will be notified and will have a button to purchase them.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1754,14 +1650,11 @@
 buy them.</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1792,14 +1685,11 @@
           <t>The system must detect whether the user has the Cintia functionality activated.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1813,14 +1703,11 @@
           <t>The system must detect if the user has the Cintia functionality activated.</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1851,14 +1738,11 @@
           <t>The behavior of the menu must be consistent with the rest of the application.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>R_25</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1872,14 +1756,11 @@
           <t>The menu's behavior must be consistent with the rest of the application.</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>CF_M04_R25</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1910,14 +1791,11 @@
           <t>The code follows a clear architecture and is reviewable via PRs without difficulty.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>R_37</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1931,14 +1809,11 @@
           <t>The code follows a clear architecture and is reviewable through PRs without difficulty.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>CF_M04_R37</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1969,14 +1844,11 @@
           <t>If the code is correct, the user must log in successfully.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1990,14 +1862,11 @@
           <t>If the code is correct, the user must log in successfully.</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2028,14 +1897,11 @@
           <t>The system must display the response progressively (typing effect).</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2049,14 +1915,11 @@
           <t>The system must display the response progressively (typing effect).</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2087,14 +1950,11 @@
           <t>The system must allow entering an email address or a phone number.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2108,14 +1968,11 @@
           <t>The system must allow entering an email address or a phone number.</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2146,14 +2003,11 @@
           <t>Each widget must load its data autonomously.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2167,14 +2021,11 @@
           <t>Each widget must load its data autonomously.</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>CF_M04_R07</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2205,14 +2056,11 @@
           <t>The user must be able to enter the received OTP code.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2226,14 +2074,11 @@
           <t>The user must be able to enter the received OTP code.</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2269,9 +2114,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2295,8 +2137,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2332,9 +2172,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2358,8 +2195,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2390,14 +2225,11 @@
           <t>The user must be able to edit or replace the suggested response.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2411,14 +2243,11 @@
           <t>The user must be able to edit or replace the suggested response.</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2449,14 +2278,11 @@
           <t>The system must display the images and videos associated with a review.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2470,14 +2296,11 @@
           <t>The system must display the images and videos associated with a review.</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>CF_M04_R20</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2508,14 +2331,11 @@
           <t>The visual layout must be consistent with the established design.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2529,14 +2349,11 @@
           <t>The visual layout must be consistent with the established design.</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>CF_M04_R07</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2567,14 +2384,11 @@
           <t>The menu must be accessible from more than one screen.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>R_25</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2588,14 +2402,11 @@
           <t>The menu must be accessible from more than one screen.</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>CF_M04_R25</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2626,14 +2437,11 @@
           <t>If the user does not see a response despite having credits, a button will appear to request the response.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2647,14 +2455,11 @@
           <t>If the user does not see a response despite having credits, a button will appear to request the response.</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2685,14 +2490,11 @@
           <t>The system must handle authentication errors and incorrect codes.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2706,14 +2508,11 @@
           <t>The system must handle authentication errors and incorrect codes.</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2744,14 +2543,11 @@
           <t>The system must send an OTP code to the indicated address or number.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2765,14 +2561,11 @@
           <t>The system must send an OTP code to the indicated address or number.</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2803,14 +2596,11 @@
           <t>The Home screen must display several independent informative widgets.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2824,14 +2614,11 @@
           <t>The Home screen must display several independent informative widgets.</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>CF_M04_R07</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2862,14 +2649,11 @@
           <t>The main functionalities can be used without errors after a first use; no external instructions are required to complete basic actions.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>R_29</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2883,14 +2667,11 @@
           <t>The main functionalities can be used without errors after a first use; no external instructions are required to complete basic actions.</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>CF_M04_R29</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2921,14 +2702,11 @@
           <t>The main calls to the backend return a response in a time perceived as acceptable by the user.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>R_33</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2942,14 +2720,11 @@
           <t>The main calls to the backend return a response in a time perceived as acceptable by the user.</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>CF_M04_R33</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
